--- a/uom/DiggsUomDictionary.xlsx
+++ b/uom/DiggsUomDictionary.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dponti/GitHub/def/uom/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74EDA9FD-8E9B-D34A-94A9-AC0AC7469996}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4D5F0B5-1BDE-004D-9E2D-27EDC55E3407}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="60160" windowHeight="32100" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
